--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-08-31).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-08-31).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-182</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>R$ 636.485,11</t>
-  </si>
-  <si>
-    <t>R$ 3.297,85
-R$ 3.358,88</t>
+183</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>R$ 639.918,24</t>
+  </si>
+  <si>
+    <t>R$ 3.298,55
+R$ 3.359,29</t>
   </si>
   <si>
     <t>5.7%
-7.7%</t>
+7.6%</t>
   </si>
   <si>
     <t>36.8</t>
   </si>
   <si>
-    <t>(2.3%)</t>
-  </si>
-  <si>
-    <t>(373.1%)</t>
-  </si>
-  <si>
-    <t>(415.3%)</t>
+    <t>(2.4%)</t>
+  </si>
+  <si>
+    <t>(370.9%)</t>
+  </si>
+  <si>
+    <t>(413.1%)</t>
   </si>
   <si>
     <t>4.3%</t>
@@ -950,10 +950,10 @@
     <t>26.5</t>
   </si>
   <si>
-    <t>73.4%</t>
-  </si>
-  <si>
-    <t>9.2%</t>
+    <t>73.3%</t>
+  </si>
+  <si>
+    <t>9.1%</t>
   </si>
   <si>
     <t>4.9</t>
@@ -8790,7 +8790,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>44</v>
@@ -8826,27 +8826,61 @@
       <c t="s" r="N58" s="4">
         <v>52</v>
       </c>
-      <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="7"/>
-      <c r="S58" s="6"/>
-      <c r="T58" s="6"/>
-      <c r="U58" s="6"/>
-      <c r="V58" s="6"/>
-      <c r="W58" s="6"/>
-      <c r="X58" s="8"/>
-      <c r="Y58" s="6"/>
-      <c r="Z58" s="6"/>
-      <c r="AA58" s="8"/>
-      <c r="AB58" s="8"/>
+      <c r="O58" s="5">
+        <v>3433.1300000000001</v>
+      </c>
+      <c r="P58" s="5">
+        <v>3433.1300000000001</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>0.010029302391263428</v>
+      </c>
+      <c r="R58" s="7">
+        <v>39</v>
+      </c>
+      <c r="S58" s="6">
+        <v>-0.15217391304347827</v>
+      </c>
+      <c r="T58" s="6">
+        <v>0.31234989645017813</v>
+      </c>
+      <c r="U58" s="6">
+        <v>-0.038592246725291497</v>
+      </c>
+      <c r="V58" s="6">
+        <v>0.015494898241546344</v>
+      </c>
+      <c r="W58" s="6">
+        <v>-0.0094065765059872467</v>
+      </c>
+      <c r="X58" s="8">
+        <v>25.015054838709677</v>
+      </c>
+      <c r="Y58" s="6">
+        <v>0.61290322580645162</v>
+      </c>
+      <c r="Z58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="8">
+        <v>5.0223684210526311</v>
+      </c>
+      <c r="AB58" s="8">
+        <v>5.3394433333333335</v>
+      </c>
       <c r="AC58" s="8">
         <v>10.530303999999999</v>
       </c>
-      <c r="AD58" s="8"/>
-      <c r="AE58" s="6"/>
+      <c r="AD58" s="8">
+        <v>17.240861290322577</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>0.77419354838709675</v>
+      </c>
       <c r="AF58" s="9"/>
-      <c r="AG58" s="5"/>
+      <c r="AG58" s="5">
+        <v>0</v>
+      </c>
       <c r="AH58" s="10">
         <v>2</v>
       </c>
@@ -17051,7 +17085,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -17444,7 +17478,7 @@
         <v>0</v>
       </c>
       <c r="AH126" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI126" s="11"/>
       <c r="AJ126" s="13">
@@ -18621,7 +18655,7 @@
         <v>-14.9</v>
       </c>
       <c r="AH135" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI135" s="11"/>
       <c r="AJ135" s="13">
@@ -20939,7 +20973,7 @@
         <v>-740.86000000000001</v>
       </c>
       <c r="AH153" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI153" s="11"/>
       <c r="AJ153" s="13">
@@ -22223,7 +22257,7 @@
         <v>-73.799999999999997</v>
       </c>
       <c r="AH163" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI163" s="11"/>
       <c r="AJ163" s="13">
@@ -24301,7 +24335,9 @@
       <c r="AB179" s="8">
         <v>1.4992409090909091</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>4.7689380000000003</v>
+      </c>
       <c r="AD179" s="8">
         <v>11.715909090909092</v>
       </c>
@@ -28386,7 +28422,7 @@
       <c r="AF212" s="9"/>
       <c r="AG212" s="5"/>
       <c r="AH212" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI212" s="11"/>
       <c r="AJ212" s="12"/>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-08-31).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-08-31).xlsx
@@ -912,48 +912,48 @@
   </si>
   <si>
     <t>214
-183</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>R$ 639.918,24</t>
-  </si>
-  <si>
-    <t>R$ 3.298,55
-R$ 3.359,29</t>
-  </si>
-  <si>
-    <t>5.7%
-7.6%</t>
-  </si>
-  <si>
-    <t>36.8</t>
-  </si>
-  <si>
-    <t>(2.4%)</t>
-  </si>
-  <si>
-    <t>(370.9%)</t>
-  </si>
-  <si>
-    <t>(413.1%)</t>
-  </si>
-  <si>
-    <t>4.3%</t>
+186</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>R$ 644.876,54</t>
+  </si>
+  <si>
+    <t>R$ 3.273,48
+R$ 3.331,76</t>
+  </si>
+  <si>
+    <t>5.5%
+7.4%</t>
+  </si>
+  <si>
+    <t>36.5</t>
+  </si>
+  <si>
+    <t>(2.3%)</t>
+  </si>
+  <si>
+    <t>(366.8%)</t>
+  </si>
+  <si>
+    <t>(409.0%)</t>
+  </si>
+  <si>
+    <t>4.4%</t>
   </si>
   <si>
     <t>0.0%</t>
   </si>
   <si>
-    <t>26.5</t>
+    <t>26.6</t>
   </si>
   <si>
     <t>73.3%</t>
   </si>
   <si>
-    <t>9.1%</t>
+    <t>9.2%</t>
   </si>
   <si>
     <t>4.9</t>
@@ -968,13 +968,13 @@
     <t>18.6</t>
   </si>
   <si>
-    <t>74.6%</t>
-  </si>
-  <si>
-    <t>-R$ 21.250,43</t>
-  </si>
-  <si>
-    <t>2.95</t>
+    <t>74.4%</t>
+  </si>
+  <si>
+    <t>-R$ 21.125,63</t>
+  </si>
+  <si>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -5994,7 +5994,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -6030,25 +6030,61 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="O36" s="5">
+        <v>2960.46</v>
+      </c>
+      <c r="P36" s="5">
+        <v>2960.46</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0.56928703949112114</v>
+      </c>
+      <c r="R36" s="7">
+        <v>41</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.95238095238095233</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.34910172743425011</v>
+      </c>
+      <c r="U36" s="6">
+        <v>0.017129669037919782</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.12476540807847429</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.059569458800321572</v>
+      </c>
+      <c r="X36" s="8">
+        <v>31.936310714285714</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>3.5581292682926828</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>8.4198730769230767</v>
+      </c>
+      <c r="AC36" s="8">
+        <v>12.402609</v>
+      </c>
+      <c r="AD36" s="8">
+        <v>18.661310714285715</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.4642857142857143</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -7913,7 +7949,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7949,25 +7985,61 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
-      <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="O51" s="5">
+        <v>247.30000000000001</v>
+      </c>
+      <c r="P51" s="5">
+        <v>247.30000000000001</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.29120091716824292</v>
+      </c>
+      <c r="R51" s="7">
+        <v>3</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.25</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.28176304084108372</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.1079296401132228</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.4097007682976142</v>
+      </c>
+      <c r="X51" s="8">
+        <v>29.649999999999999</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>6.6833333333333336</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>14.0167</v>
+      </c>
+      <c r="AC51" s="8">
+        <v>18.633331999999999</v>
+      </c>
+      <c r="AD51" s="8">
+        <v>25.449999999999999</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>1</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -12672,7 +12744,7 @@
         <v>0</v>
       </c>
       <c r="AH88" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI88" s="11"/>
       <c r="AJ88" s="13">
@@ -12711,7 +12783,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12745,25 +12817,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>1750.54</v>
+      </c>
+      <c r="P89" s="5">
+        <v>1750.54</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.52308509623898325</v>
+      </c>
+      <c r="R89" s="7">
+        <v>19</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.52500000000000002</v>
+      </c>
+      <c r="T89" s="6">
+        <v>3.8882592799936018</v>
+      </c>
+      <c r="U89" s="6">
+        <v>3.5409093194100105</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.059142893050144529</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.0034743564842848493</v>
+      </c>
+      <c r="X89" s="8">
+        <v>31.5083375</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.125</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>3.0379611111111111</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>14.958333333333334</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>21.2416625</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.5</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>124.8</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -16823,7 +16929,7 @@
         <v>0</v>
       </c>
       <c r="AH121" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI121" s="11"/>
       <c r="AJ121" s="13">
@@ -18786,7 +18892,7 @@
         <v>-61.899999999999999</v>
       </c>
       <c r="AH136" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI136" s="11"/>
       <c r="AJ136" s="13">
@@ -21100,7 +21206,7 @@
         <v>0</v>
       </c>
       <c r="AH154" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI154" s="11"/>
       <c r="AJ154" s="13">
